--- a/260724_松本大介TTP_資格覇者分析と首席逆算_v1.xlsx
+++ b/260724_松本大介TTP_資格覇者分析と首席逆算_v1.xlsx
@@ -25,12 +25,77 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="240">
   <si>
     <t xml:space="preserve">司法書士法人ネクストリーガル 松本大介氏 — 人物・会社分析</t>
   </si>
   <si>
-    <t xml:space="preserve">作成: 2026-07-24（アガルート測量士・測量士補 合格祝賀会 翌朝整理）／出典: 名刺・本人談・Web公開情報</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">作成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 2026-07-24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（アガルート測量士・測量士補 合格祝賀会 翌朝整理）／出典</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名刺・本人談・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Web</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公開情報</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">項目</t>
@@ -63,16 +128,148 @@
     <t xml:space="preserve">法人名</t>
   </si>
   <si>
-    <t xml:space="preserve">司法書士法人ネクストリーガル（NEXT LEGAL）／行政書士事務所ネクストリーガル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">名刺・Web</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">司法書士法人ネクストリーガル（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NEXT LEGAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）／行政書士事務所ネクストリーガル</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名刺・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Web</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">所在地</t>
   </si>
   <si>
-    <t xml:space="preserve">〒150-0021 東京都渋谷区恵比寿西1-12-12 ルネスE.B.I 5F（JR恵比寿駅西口 徒歩3分）</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">150-0021 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">東京都渋谷区恵比寿西</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1-12-12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ルネス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E.B.I 5F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">恵比寿駅西口 徒歩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">連絡先</t>
@@ -252,7 +449,31 @@
     <t xml:space="preserve">司法書士登録</t>
   </si>
   <si>
-    <t xml:space="preserve">東京司法書士会 登録番号6800号</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">東京司法書士会 登録番号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6800</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">東京司法書士会 会員検索</t>
@@ -276,18 +497,106 @@
     <t xml:space="preserve">本業。権利登記（保存・移転・抵当権設定）＝マンション分譲の川下を全部取れる</t>
   </si>
   <si>
+    <t xml:space="preserve">土地家屋調査士（本人談・保有と判明）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">表題登記の申請代理は調査士の独占業務。「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部屋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部屋」を自ら受任できる法的根拠はこれ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">測量士（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">合格・今回の祝賀会）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">表題の前工程＝測量まで内製化。調査士業務を外注ゼロで回す布石</t>
+  </si>
+  <si>
     <t xml:space="preserve">行政書士</t>
   </si>
   <si>
     <t xml:space="preserve">許認可・宗教法人関係の手続に接続。太客（宗教法人）案件の入口</t>
   </si>
   <si>
-    <t xml:space="preserve">測量士（2026合格・今回の祝賀会）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">表題登記の川上へ進出。調査士業務との連携・測量まで内製化する布石</t>
-  </si>
-  <si>
     <t xml:space="preserve">測量士補</t>
   </si>
   <si>
@@ -297,19 +606,142 @@
     <t xml:space="preserve">マンション管理士</t>
   </si>
   <si>
-    <t xml:space="preserve">マンション3点セットその1。デベロッパー・管理組合との会話力</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">マンション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点セットその</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。デベロッパー・管理組合との会話力</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">管理業務主任者</t>
   </si>
   <si>
-    <t xml:space="preserve">マンション3点セットその2。管理会社サイドの実務知識</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">マンション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点セットその</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。管理会社サイドの実務知識</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">宅地建物取引士</t>
   </si>
   <si>
-    <t xml:space="preserve">マンション3点セットその3。売買実務・デベロッパーの商流理解</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">マンション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点セットその</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。売買実務・デベロッパーの商流理解</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">貸金業務取扱主任者</t>
@@ -363,16 +795,222 @@
     <t xml:space="preserve">相続・資産の入口商談で顧客の全体像を掴む</t>
   </si>
   <si>
-    <t xml:space="preserve">★構造分析: 「マンション3資格×登記2資格（司法書士＋測量士）」の掛け算で、新築マンション一棟案件を表題（川上）から権利（川下）までワンストップ受注できる稀有なポジション。資格リストそのものが営業資料になっている。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">出典URL: https://www.tokyokai.jp/tokyokai/member03.php?id=11-00607 ／ https://info.gbiz.go.jp/hojin/ichiran?hojinBango=1011005009537 ／ https://office-nl.com/about/ ／ https://nextlegal.jp/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">松本メソッド（阪大生直伝の過去問法＋出題者分析）— 分解とTTP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">祝賀会での本人談を分解。「型→原理→俺の現状→今日からの実装」の4段で写経する</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">★構造分析</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「マンション</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資格</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">登記</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資格（司法書士＋調査士＋測量士）」の掛け算で、新築マンション一棟案件を測量→表題（調査士の独占業務）→権利（川下）までワンストップ受注できる稀有なポジション。資格リストそのものが営業資料になっている。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">出典</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">URL: https://www.tokyokai.jp/tokyokai/member03.php?id=11-00607 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">https://info.gbiz.go.jp/hojin/ichiran?hojinBango=1011005009537 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">https://office-nl.com/about/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">https://nextlegal.jp/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">松本メソッド（阪大生直伝の過去問法＋出題者分析）— 分解と</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TTP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">祝賀会での本人談を分解。「型→原理→俺の現状→今日からの実装」の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段で写経する</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">松本の型（本人談）</t>
@@ -384,13 +1022,84 @@
     <t xml:space="preserve">俺の現状</t>
   </si>
   <si>
-    <t xml:space="preserve">今日からのTTP実装</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今日からの</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TTP</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実装</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">運用場所</t>
   </si>
   <si>
-    <t xml:space="preserve">過去問は4〜5周目まで線を引かない・マークしない。「理解できた・知識が紐づいてきた」と感じるまで待つ</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">過去問は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周目まで線を引かない・マークしない。「理解できた・知識が紐づいてきた」と感じるまで待つ</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">早期マーキングは「作業した感」を生む偽の達成感。理解前のラベルはノイズ。まず知識ネットワーク化を優先</t>
@@ -438,7 +1147,31 @@
     <t xml:space="preserve">chosashi_kakomon_tracker_H17-26.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">紐づいた後は「どうしても間違う問題だけ」に○×△を付けていく</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">紐づいた後は「どうしても間違う問題だけ」に○</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×△</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を付けていく</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">全問管理をやめてエラーだけ管理＝管理コスト最小化。弱点だけが浮き上がる</t>
@@ -463,28 +1196,241 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">トラッカーは「×が出た問題だけ」記入に運用変更。全問埋めない</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">トラッカーは「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が出た問題だけ」記入に運用変更。全問埋めない</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">同トラッカー</t>
   </si>
   <si>
-    <t xml:space="preserve">○が3回付いた問題は二度と解かない</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">○が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回付いた問題は二度と解かない</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">卒業基準の明文化。復習母集団が単調減少→直前期が自動的に軽くなる</t>
   </si>
   <si>
-    <t xml:space="preserve">卒業基準なし。Ankiのdueが無限に湧いて圧迫感</t>
-  </si>
-  <si>
-    <t xml:space="preserve">トラッカーに「卒業」判定を追加（○3回=以後封印）。Ankiも3連続正解カードはsuspend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">トラッカー＋Anki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「R5はクソ問だから解くなと言われるが、むしろ順に解けば素直。『法務省の犬として素直に順に解けるか』を問われている」</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">卒業基準なし。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Anki</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が無限に湧いて圧迫感</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">トラッカーに「卒業」判定を追加（○</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以後封印）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Anki</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">も</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">連続正解カードは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">suspend</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">トラッカー＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Anki</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">R5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">はクソ問だから解くなと言われるが、むしろ順に解けば素直。『法務省の犬として素直に順に解けるか』を問われている」</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">教材や予備校の評判（二次情報）より問題そのもの（一次情報）で判断。出題者の真意を読むメタ認知＝営業のヒアリング力と同型</t>
@@ -493,19 +1439,149 @@
     <t xml:space="preserve">予備校の攻略法・評判を鵜呑みにしがち。年度通しの「出題者との対話」をしていない</t>
   </si>
   <si>
-    <t xml:space="preserve">年度別通し演習のたびに「この年の出題者は何を試したか」を1行で言語化して残す</t>
-  </si>
-  <si>
-    <t xml:space="preserve">週1本番形式のあと5分</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年度別通し演習のたびに「この年の出題者は何を試したか」を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行で言語化して残す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本番形式のあと</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">阪大生に聴いた勉強法を、自己流を挟まず素直に実行</t>
   </si>
   <si>
-    <t xml:space="preserve">強者の型を探す→そのままやる（NIH症候群なし）。TTP力そのものが最強の学習スキル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">俺も今このシートでTTP中。ただし俺は型を「改造」したくなる癖がある</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">強者の型を探す→そのままやる（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NIH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">症候群なし）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TTP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">力そのものが最強の学習スキル</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">俺も今このシートで</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TTP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中。ただし俺は型を「改造」したくなる癖がある</t>
+    </r>
   </si>
   <si>
     <r>
@@ -530,25 +1606,338 @@
     <t xml:space="preserve">本シート＋週次レビュー</t>
   </si>
   <si>
-    <t xml:space="preserve">資格を連鎖取得（司法書士→行政書士→宅建→マン管→…→測量士）し、1本ずつ商流に接続</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「解くな」と言われる令和</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年の記述も、評判で捨てず、出題者が何を要求しているかを素直に順に処理して向き合った（本人談・考え方が秀逸）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">記述でも択一と同じ一次情報主義。『捨て問』の評判は他人の敗因の集計であって、自分の戦略ではない。要求を分解すれば部分点は積める</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">予備校の『捨て問』ラベルに無条件で従う前提でいた。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">R5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">記述は解かないつもりだった</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">R5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">記述を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）で本番形式で解き、「出題者は何を要求したか」を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行言語化。捨てるかどうかは自分の答案で判断</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">⑤P4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仕上</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資格を連鎖取得（司法書士→行政書士→宅建→マン管→…→調査士→測量士）し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本ずつ商流に接続</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">資格＝知識コレクションではなく商流の関所。取るたびに受注範囲が川上へ伸びる</t>
   </si>
   <si>
-    <t xml:space="preserve">調査士挑戦中（10/18）。合格後の商流接続イメージが薄い</t>
-  </si>
-  <si>
-    <t xml:space="preserve">調査士合格＝KHD不動産事業の表題側参入と定義（⑤シートの北極星）</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">調査士挑戦中（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。合格後の商流接続イメージが薄い</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">調査士合格＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KHD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不動産事業の表題側参入と定義（⑤シートの北極星）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">⑤首席逆算</t>
   </si>
   <si>
-    <t xml:space="preserve">松本氏の収益モデル — 新築マンション一棟×表題登記のユニットエコノミクス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">数値は祝賀会での本人談ベース（青字＝仮定・入力値）。凡例: 青字=入力値／黒字=計算式</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">松本氏の収益モデル — 新築マンション一棟</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">表題登記のユニットエコノミクス</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">数値は祝賀会での本人談ベース（青字＝仮定・入力値）。凡例</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">青字</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">入力値／黒字</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">計算式</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">数値</t>
@@ -558,18 +1947,6 @@
   </si>
   <si>
     <t xml:space="preserve">表題登記 単価／部屋</t>
-  </si>
-  <si>
-    <t xml:space="preserve">本人談「1部屋10万で表題入れたとして」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">部屋数／棟</t>
-  </si>
-  <si>
-    <t xml:space="preserve">本人談「100部屋で1000万」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">売上／棟（表題のみ）</t>
   </si>
   <si>
     <r>
@@ -579,7 +1956,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">＝単価</t>
+      <t xml:space="preserve">本人談「</t>
     </r>
     <r>
       <rPr>
@@ -589,7 +1966,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">×</t>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
@@ -598,38 +1975,32 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">部屋数</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">受注ペース（棟／年）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">本人談「3ヶ月に一棟ペースを見込める」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">年間売上（表題のみ）</t>
-  </si>
-  <si>
+      <t xml:space="preserve">部屋</t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＝棟売上</t>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×</t>
-    </r>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万で表題入れたとして」</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">部屋数／棟</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -637,6 +2008,143 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">本人談「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部屋で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万」</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">売上／棟（表題のみ）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝単価</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部屋数</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">受注ペース（棟／年）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本人談「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ヶ月に一棟ペースを見込める」</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">年間売上（表題のみ）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝棟売上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">年間棟数</t>
     </r>
   </si>
@@ -650,13 +2158,152 @@
     <t xml:space="preserve">中身</t>
   </si>
   <si>
-    <t xml:space="preserve">俺（KHD）への示唆</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">俺（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KHD</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）への示唆</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">川上グリップ</t>
   </si>
   <si>
-    <t xml:space="preserve">デベロッパー1社を握れば、1棟＝100部屋の登記が「自動で」100件発生。1契約×反復の構造</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">デベロッパー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社を握れば、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">棟＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部屋の登記が「自動で」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件発生。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">契約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">反復の構造</t>
+    </r>
   </si>
   <si>
     <r>
@@ -732,16 +2379,81 @@
     <t xml:space="preserve">ワンストップ独占</t>
   </si>
   <si>
-    <t xml:space="preserve">表題（測量士・調査士側）→保存・移転・設定（司法書士側）まで同一法人で完結。他士業に商流が漏れない</t>
-  </si>
-  <si>
-    <t xml:space="preserve">俺の調査士合格＝表題側への参入資格。KHDの医療×不動産も「紹介で外に出さない」設計へ</t>
+    <t xml:space="preserve">測量（測量士）→表題登記の申請代理（調査士の独占業務・本人が保有）→保存・移転・設定（司法書士）まで同一法人で完結。他士業に商流が一切漏れない</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">俺の調査士合格＝表題側への参入資格。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KHD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の医療</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不動産も「紹介で外に出さない」設計へ</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">太客ポートフォリオ</t>
   </si>
   <si>
-    <t xml:space="preserve">宗教法人からの案件＋多様な取引太客をグリップ。相続（office-nl.comの看板）も宗教法人・資産家と親和</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">宗教法人からの案件＋多様な取引太客をグリップ。相続（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">office-nl.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の看板）も宗教法人・資産家と親和</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">顧客マスターから「反復発注を構造化できる太客」を選定して深耕（④シートで実行）</t>
@@ -765,7 +2477,58 @@
     <t xml:space="preserve">勉強でメタ読みを鍛える＝商談の筋トレと捉える。④の送信前チェック・黙る力と接続</t>
   </si>
   <si>
-    <t xml:space="preserve">俺の課題 × 松本・宮崎の型 → 今日からのTTPアクション</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">俺の課題 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">松本・宮崎の型 → 今日からの</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TTP</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">アクション</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">宮崎類似＝「相手の真意を掴む分析力→速く出して握る」。稼ぐ人の共通型として統合</t>
@@ -809,7 +2572,31 @@
     <t xml:space="preserve">期限</t>
   </si>
   <si>
-    <t xml:space="preserve">答練・模試 未実施で実力が測定不能（「正答率70%くらい」としか言えず、りょーさんに落ちこぼれ側と括られた）</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">答練・模試 未実施で実力が測定不能（「正答率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">くらい」としか言えず、りょーさんに落ちこぼれ側と括られた）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">祝賀会二次会での会話</t>
@@ -818,7 +2605,65 @@
     <t xml:space="preserve">松本＝出題者と対話できるレベルまで過去問で測定し切る</t>
   </si>
   <si>
-    <t xml:space="preserve">答練に今週申込み、8月第1週に初回受験。以後は週1本番形式で必ず「点数」を出す</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">答練に今週申込み、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週に初回受験。以後は週</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本番形式で必ず「点数」を出す</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">答練・模試の点数と順位を毎回記録</t>
@@ -830,16 +2675,129 @@
     <t xml:space="preserve">勉強量の絶対不足（答練前提の同志・仙台の首席候補との差）</t>
   </si>
   <si>
-    <t xml:space="preserve">りょーさん（@ryofeat）談</t>
-  </si>
-  <si>
-    <t xml:space="preserve">資格覇者は型を決めて淡々と回す（10資格分の実証）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">既存プラン（朝1.6h記述＋Anki隙間）の実施率を週次で管理。増やすより「落とさない」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">週次実施率90%以上</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">りょーさん（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">@ryofeat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）談</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資格覇者は型を決めて淡々と回す（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資格分の実証）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">既存プラン（朝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.6h</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">記述＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Anki</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">隙間）の実施率を週次で管理。増やすより「落とさない」</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週次実施率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">90%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以上</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">毎週日曜</t>
@@ -851,13 +2809,119 @@
     <t xml:space="preserve">秘書室レーダー／空欄のトラッカー</t>
   </si>
   <si>
-    <t xml:space="preserve">松本＝5周目まで線を引かない（仕組みより回転）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">トラッカー運用を「×のみ記入・○3回で卒業」に簡素化。新しい管理ツールは作らない</t>
-  </si>
-  <si>
-    <t xml:space="preserve">トラッカー記入時間 5分/日以内</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">松本＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周目まで線を引かない（仕組みより回転）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">トラッカー運用を「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のみ記入・○</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回で卒業」に簡素化。新しい管理ツールは作らない</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">トラッカー記入時間 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日以内</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">今日</t>
@@ -866,22 +2930,135 @@
     <t xml:space="preserve">相手の真意を掴む前に喋る・出しすぎ・先回りしすぎ</t>
   </si>
   <si>
-    <t xml:space="preserve">江藤レポート／LINE43本実証</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">江藤レポート／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LINE43</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本実証</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">松本＝出題者の真意すら読む。宮崎＝相手の合格点を掴んで速く出して握る</t>
   </si>
   <si>
-    <t xml:space="preserve">送信前3秒チェック継続＋商談は「相手の合格点を先に聞く」。祝賀会のように「相手に持論を語らせる」側に回る</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黙る力5問 4YES以上／日</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">送信前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">秒チェック継続＋商談は「相手の合格点を先に聞く」。祝賀会のように「相手に持論を語らせる」側に回る</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">黙る力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">問 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4YES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以上／日</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">毎晩</t>
   </si>
   <si>
-    <t xml:space="preserve">太客・反復構造の欠如（1件ずつ追客する狩猟型で消耗）</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">太客・反復構造の欠如（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件ずつ追客する狩猟型で消耗）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">③収益モデル比較で判明</t>
@@ -890,7 +3067,48 @@
     <t xml:space="preserve">松本＝デベロッパー・宗教法人を握り反復案件を自動発生させる</t>
   </si>
   <si>
-    <t xml:space="preserve">顧客マスターから「反復発注を構造化できる太客」候補を3社選定→深耕プラン1枚</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顧客マスターから「反復発注を構造化できる太客」候補を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社選定→深耕プラン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">枚</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">反復構造の締結数／四半期</t>
@@ -902,16 +3120,114 @@
     <t xml:space="preserve">未確定の合否・数字を口に出すビッグマウス</t>
   </si>
   <si>
-    <t xml:space="preserve">黙る力5問#2</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">黙る力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">問</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#2</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">松本＝合格してから祝賀会で語る（実績→発信の順）</t>
   </si>
   <si>
-    <t xml:space="preserve">「首席を狙う」は内なる火。外にはアンダーコミット（10/18までSNS・他人への宣言禁止）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">違反0回</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「首席を狙う」は内なる火。外にはアンダーコミット（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">まで</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SNS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・他人への宣言禁止）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">違反</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">毎日</t>
@@ -923,19 +3239,219 @@
     <t xml:space="preserve">温度感ログ⚡の既知パターン</t>
   </si>
   <si>
-    <t xml:space="preserve">松本＝3ヶ月に1棟のペース設計＝焦らず構造で勝つ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">焦りを感じたら新規タスクではなく「今日の記述1問」に変換するルール</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">松本＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ヶ月に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">棟のペース設計＝焦らず構造で勝つ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">焦りを感じたら新規タスクではなく「今日の記述</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">問」に変換するルール</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">⚡検知時の記述変換率</t>
   </si>
   <si>
-    <t xml:space="preserve">土地家屋調査士 2026-10-18 首席逆算プラン（残り86日）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">既存の満点計画（P3通す→P4仕上→P5直前）に松本メソッドと答練を上書き。青字=入力値</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">土地家屋調査士 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-18 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">首席逆算プラン（残り</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">86</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">既存の満点計画（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">通す→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仕上→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">直前）に松本メソッドと答練を上書き。青字</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">入力値</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">本試験日</t>
@@ -956,7 +3472,37 @@
     <t xml:space="preserve">机の主役（記述）</t>
   </si>
   <si>
-    <t xml:space="preserve">隙間（Anki/択一）</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">隙間（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Anki/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">択一）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">松本メソッド適用</t>
@@ -987,13 +3533,102 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">記述1日1問（時間計測を開始）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">弱点3-4位（添付・床面積）継続</t>
-  </si>
-  <si>
-    <t xml:space="preserve">トラッカー運用開始＝×のみ記入。マーキングは紐づいた分野だけ解禁</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">記述</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">問（時間計測を開始）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">弱点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3-4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位（添付・床面積）継続</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">トラッカー運用開始＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のみ記入。マーキングは紐づいた分野だけ解禁</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">答練を今週申込（最重要）</t>
@@ -1021,10 +3656,109 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">土地50分/建物50分の時間内完答へ。週1本番形式</t>
-  </si>
-  <si>
-    <t xml:space="preserve">弱点5-10位を順に＋全体維持</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">土地</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">建物</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分の時間内完答へ。週</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本番形式</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">弱点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5-10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位を順に＋全体維持</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1080,7 +3814,48 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">答練初回8月第1週→隔週。点数・順位を④に記録</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">答練初回</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週→隔週。点数・順位を④に記録</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">9/1-9/30</t>
@@ -1105,7 +3880,48 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">記述はR01-06の新しめ中心</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">記述は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">R01-06</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の新しめ中心。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">R5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">も捨てずに本番形式で解く（松本流：出題者の要求を順に処理→部分点を積む）</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1142,11 +3958,69 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">回の問題を続々「卒業」させ復習母集団を圧縮</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">模試・答練を本番同様に。首席狙い＝択一の取りこぼし0を意識</t>
+      <t xml:space="preserve">回の問題を続々「卒業」させ復習母集団を圧縮。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">R5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">記述の「出題者は何を要求したか」を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行言語化</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">模試・答練を本番同様に。首席狙い＝択一の取りこぼし</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を意識</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">10/1-10/17</t>
@@ -1208,19 +4082,146 @@
     <t xml:space="preserve">―</t>
   </si>
   <si>
-    <t xml:space="preserve">「出題者の犬として素直に、順に解く」。難問の評判に惑わされず1問目から順に</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「出題者の犬として素直に、順に解く」。難問の評判に惑わされず</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">問目から順に</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">首席は結果。狙いは満点行動の積分</t>
   </si>
   <si>
-    <t xml:space="preserve">★りょーさん（@ryofeat・29歳・仙台の首席候補と接点）への競争心は燃料としてのみ使う。外に出すのは合格後。差の正体は「答練で測定しているか」だけ＝今週の申込で埋まる差。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">今日から動く — チェックリスト（TODO形式）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">終わったら✔。秘書室TODO形式と同じ「タスク｜優先度｜期限」</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">★りょーさん（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">@ryofeat</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">29</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳・仙台の首席候補と接点）への競争心は燃料としてのみ使う。外に出すのは合格後。差の正体は「答練で測定しているか」だけ＝今週の申込で埋まる差。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今日から動く — チェックリスト（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TODO</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">形式）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">終わったら✔。秘書室</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TODO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">形式と同じ「タスク｜優先度｜期限」</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">✔</t>
@@ -1232,7 +4233,31 @@
     <t xml:space="preserve">優先度</t>
   </si>
   <si>
-    <t xml:space="preserve">答練（アガルートor東京法経）の申込を完了する</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">答練（アガルート</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">or</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">東京法経）の申込を完了する</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">高</t>
@@ -1241,16 +4266,139 @@
     <t xml:space="preserve">2026-07-27</t>
   </si>
   <si>
-    <t xml:space="preserve">トラッカー運用を「×のみ記入・○3回で卒業」に変更して今日の1問から開始</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">トラッカー運用を「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のみ記入・○</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回で卒業」に変更して今日の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">問から開始</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">2026-07-24</t>
   </si>
   <si>
-    <t xml:space="preserve">今日の記述1問（時間計測）— 焦りは全部ここに変換</t>
-  </si>
-  <si>
-    <t xml:space="preserve">松本氏へお礼連絡（名刺のMailへ短文3文以内・問いで終える。二次会の御礼＋調査士合格後に改めて挨拶したい旨）</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今日の記述</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">問（時間計測）— 焦りは全部ここに変換</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">松本氏へお礼連絡（名刺の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mail</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へ短文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">文以内・問いで終える。二次会の御礼＋調査士合格後に改めて挨拶したい旨）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">通常</t>
@@ -1259,13 +4407,61 @@
     <t xml:space="preserve">2026-07-26</t>
   </si>
   <si>
-    <t xml:space="preserve">りょーさん（LINE/X @ryofeat）へ二次会の御礼を短文で（勝負心は書かない）</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">りょーさん（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LINE/X @ryofeat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）へ二次会の御礼を短文で（勝負心は書かない）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">2026-07-25</t>
   </si>
   <si>
-    <t xml:space="preserve">顧客マスターから「反復発注を構造化できる太客」候補3社を選ぶ</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顧客マスターから「反復発注を構造化できる太客」候補</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社を選ぶ</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">2026-08-01</t>
@@ -1274,7 +4470,72 @@
     <t xml:space="preserve">週次レビュー（日曜）に「答練点数」「トラッカー卒業数」「出題者の意図メモ」を追加</t>
   </si>
   <si>
-    <t xml:space="preserve">※ お礼連絡は送信前3秒チェック（3文ルール・問いで終える・絵文字2個以内）を通してから。</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ お礼連絡は送信前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">秒チェック（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">文ルール・問いで終える・絵文字</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個以内）を通してから。</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1318,13 +4579,18 @@
       <color rgb="FF1F3864"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Yu Gothic"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1333,13 +4599,11 @@
       <color rgb="FFFFFFFF"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1348,17 +4612,11 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FFBF9000"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1373,6 +4631,12 @@
       <sz val="10"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Yu Gothic"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1380,25 +4644,25 @@
       <color rgb="FF808080"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF808080"/>
+      <name val="Yu Gothic"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF1F3864"/>
+      <name val="Yu Gothic"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
-      <name val="Yu Gothic"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF595959"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
       <name val="Yu Gothic"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1415,13 +4679,6 @@
       <name val="Yu Gothic"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -1507,33 +4764,21 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1544,7 +4789,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1556,47 +4809,43 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1852,264 +5101,275 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="94"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+    <row r="7" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+    <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+    <row r="9" customFormat="false" ht="38.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="50.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+    <row r="10" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+    <row r="12" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="n">
+    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12" t="s">
+      <c r="C26" s="4" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="11" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2126,165 +5386,185 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="n">
+      <c r="E4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
+      <c r="E5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="8" t="s">
+      <c r="B6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="n">
+      <c r="E6" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="n">
+      <c r="E7" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="n">
+      <c r="E8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="C9" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
+      <c r="E9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>89</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2306,157 +5586,157 @@
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="46"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B5" s="13" t="n">
+      <c r="B4" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="12" t="n">
         <v>100000</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" s="15" t="n">
+      <c r="C5" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" s="16" t="n">
+      <c r="C6" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="15" t="n">
         <f aca="false">B5*B6</f>
         <v>10000000</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B8" s="18" t="n">
+      <c r="C7" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B9" s="16" t="n">
+      <c r="C8" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" s="15" t="n">
         <f aca="false">B7*B8</f>
         <v>40000000</v>
       </c>
-      <c r="C9" s="17" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C13" s="7" t="s">
+      <c r="C9" s="13" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="B14" s="6" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="B12" s="3" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+      <c r="C12" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B15" s="5" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="C13" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B16" s="6" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B17" s="5" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>122</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2478,207 +5758,207 @@
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="n">
+      <c r="B4" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
+      <c r="B5" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="n">
+      <c r="B6" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="n">
+      <c r="B7" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="n">
+      <c r="B8" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
+      <c r="B9" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="n">
+      <c r="B10" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>166</v>
+      <c r="B11" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -2700,180 +5980,180 @@
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="B4" s="20" t="n">
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="B4" s="18" t="n">
         <f aca="false">DATE(2026,10,18)</f>
         <v>46313</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="B5" s="21" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="B5" s="19" t="n">
         <f aca="false">DATE(2026,7,24)</f>
         <v>46227</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="B6" s="22" t="n">
+    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" s="20" t="n">
         <f aca="false">B4-B5</f>
         <v>86</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="B9" s="7" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="E8" s="3" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="F8" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B10" s="8" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="B9" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="D9" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="E9" s="4" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+      <c r="F9" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="B11" s="7" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="B10" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="C10" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="D10" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="E10" s="7" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+      <c r="F10" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="B12" s="8" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="B11" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="C11" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="D11" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="E11" s="6" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="F11" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="B13" s="5" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="B12" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="D12" s="7" t="s">
         <v>211</v>
       </c>
+      <c r="E12" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
+      <c r="A15" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2897,123 +6177,123 @@
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="70"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="D5" s="7" t="s">
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="D6" s="8" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6" t="s">
+      <c r="C4" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="D4" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="C5" s="4" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="D9" s="7" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6" t="s">
+      <c r="C6" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="D10" s="8" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5" t="s">
+      <c r="C7" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="C8" s="5" t="s">
         <v>232</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
